--- a/data/trans_orig/cron_prev_index-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la prevalencia</t>
+          <t>Índice de cronicidad física en base a la prevalencia (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 0,89</t>
+          <t>0,77; 0,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,27 +726,27 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,07</t>
+          <t>0,92; 1,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,33</t>
+          <t>1,09; 1,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,24</t>
+          <t>1,1; 1,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,39</t>
+          <t>1,24; 1,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,37</t>
+          <t>1,2; 1,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,22</t>
+          <t>1,1; 1,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,54</t>
+          <t>1,4; 1,53</t>
         </is>
       </c>
     </row>
@@ -861,24 +861,24 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,29; 0,35</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,36; 0,42</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,36; 0,6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0,3; 0,36</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 0,42</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 0,6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 0,36</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0,32; 0,39</t>
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,4</t>
+          <t>0,56; 1,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,36</t>
+          <t>0,31; 0,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,03</t>
+          <t>0,52; 1,02</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,6</t>
+          <t>0,48; 0,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,38</t>
+          <t>0,25; 0,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,39</t>
+          <t>0,27; 0,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,58</t>
+          <t>0,47; 0,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,34</t>
+          <t>0,25; 0,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,57</t>
+          <t>0,48; 0,57</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,57</t>
+          <t>0,51; 0,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,69</t>
+          <t>0,48; 0,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0,62; 0,68</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,67; 0,74</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>0,62; 0,69</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 0,74</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 0,69</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,78; 1,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,57</t>
+          <t>0,53; 0,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,61</t>
+          <t>0,57; 0,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,0</t>
+          <t>0,69; 0,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_prev_index-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 0,9</t>
+          <t>0,77; 0,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,16</t>
+          <t>1,0; 1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,08</t>
+          <t>0,91; 1,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,3</t>
+          <t>1,05; 1,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,23</t>
+          <t>1,1; 1,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 1,73</t>
+          <t>1,55; 1,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,07</t>
+          <t>0,98; 1,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,53</t>
+          <t>1,36; 1,49</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,57</t>
         </is>
       </c>
     </row>
@@ -861,17 +861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,35</t>
+          <t>0,3; 0,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,42</t>
+          <t>0,35; 0,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,6</t>
+          <t>0,54; 0,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,47</t>
+          <t>0,4; 0,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,32</t>
+          <t>0,52; 0,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,36</t>
+          <t>0,32; 0,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,02</t>
+          <t>0,54; 0,6</t>
         </is>
       </c>
     </row>
@@ -943,34 +943,34 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,29</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0,3</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,39</t>
+          <t>0,25; 0,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,45</t>
+          <t>0,32; 0,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,61</t>
+          <t>0,49; 0,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,36</t>
+          <t>0,25; 0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,39</t>
+          <t>0,28; 0,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,57</t>
+          <t>0,48; 0,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,57</t>
+          <t>0,5; 0,59</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,57</t>
+          <t>0,5; 0,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,68</t>
+          <t>0,63; 0,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,68</t>
+          <t>0,62; 0,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,31</t>
+          <t>0,76; 0,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,98</t>
+          <t>0,71; 0,75</t>
         </is>
       </c>
     </row>
